--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484564_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484564_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7012</v>
+        <v>6.4656</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2123</v>
+        <v>2.7289</v>
       </c>
       <c r="F2" t="n">
-        <v>3.489</v>
+        <v>3.7367</v>
       </c>
       <c r="G2" t="n">
         <v>4.4652</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1969</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0121</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1847</v>
+        <v>0.4325</v>
       </c>
       <c r="V2" t="n">
         <v>1.5889</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1244</v>
+        <v>5.5996</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5581</v>
+        <v>3.1324</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5663</v>
+        <v>2.4672</v>
       </c>
       <c r="G3" t="n">
         <v>3.306</v>
@@ -688,13 +688,13 @@
         <v>3.2986</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6926</v>
+        <v>1.1678</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7851</v>
+        <v>0.3594</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9075</v>
+        <v>0.8084</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2566</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2818</v>
+        <v>0.0376</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2702</v>
+        <v>-0.4897</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5521</v>
+        <v>0.5273</v>
       </c>
       <c r="G4" t="n">
         <v>0.5269</v>
@@ -766,13 +766,13 @@
         <v>2.3823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2005</v>
+        <v>-0.4448</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6252</v>
+        <v>-0.8446</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4246</v>
+        <v>0.3999</v>
       </c>
       <c r="V4" t="n">
         <v>0.3219</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.7516</v>
+        <v>-1.1757</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.1712</v>
+        <v>-1.4727</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4196</v>
+        <v>0.297</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1531</v>
+        <v>-1.7891</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3452</v>
+        <v>0.285</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1922</v>
+        <v>-2.0742</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.6229</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9819</v>
+        <v>1.1704</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.641</v>
+        <v>-0.5994</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4698</v>
+        <v>-2.3602</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3633</v>
+        <v>-0.8854</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8332000000000001</v>
+        <v>-1.4748</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1991</v>
+        <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3019</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7157</v>
+        <v>-0.5332</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0176</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.267</v>
+        <v>-0.3115</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8411</v>
+        <v>-1.5626</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.863</v>
+        <v>-3.6353</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9781</v>
+        <v>2.0727</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6714</v>
+        <v>-1.1531</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3251</v>
+        <v>-1.3452</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3463</v>
+        <v>0.1922</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5327</v>
+        <v>-1.6229</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1084</v>
+        <v>-0.9819</v>
       </c>
       <c r="L6" t="n">
         <v>-0.641</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1388</v>
+        <v>0.4698</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4335</v>
+        <v>-0.3633</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7053</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3138</v>
+        <v>0.4909</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3303</v>
+        <v>-0.1798</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0165</v>
+        <v>0.6708</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9732</v>
+        <v>-1.6651</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0225</v>
+        <v>-0.7118</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0493</v>
+        <v>-0.9534</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7891</v>
+        <v>-1.6714</v>
       </c>
       <c r="H7" t="n">
-        <v>0.285</v>
+        <v>-0.3251</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0742</v>
+        <v>-1.3463</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5711000000000001</v>
+        <v>-0.5327</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1704</v>
+        <v>0.1084</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5994</v>
+        <v>-0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3602</v>
+        <v>-1.1388</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8854</v>
+        <v>-0.4335</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4748</v>
+        <v>-0.7053</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7489</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.1378</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0829</v>
+        <v>-0.1791</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2941</v>
+        <v>0.0413</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3115</v>
+        <v>-0.9554</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6335</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4139</v>
+        <v>-3.0812</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.1445</v>
+        <v>-4.787</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7306</v>
+        <v>1.7058</v>
       </c>
       <c r="G8" t="n">
         <v>-4.7292</v>
@@ -1078,13 +1078,13 @@
         <v>2.1991</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9516</v>
+        <v>-0.619</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2481</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2964</v>
+        <v>0.2717</v>
       </c>
       <c r="V8" t="n">
         <v>1.9005</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8149</v>
+        <v>-3.46</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0814</v>
+        <v>-4.8752</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2665</v>
+        <v>1.4151</v>
       </c>
       <c r="G9" t="n">
         <v>-3.767</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2312</v>
+        <v>0.1237</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2398</v>
+        <v>-0.0335</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0086</v>
+        <v>0.1572</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.278</v>
+        <v>-3.8273</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4126</v>
+        <v>-4.8628</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1347</v>
+        <v>1.0356</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2299</v>
@@ -1234,13 +1234,13 @@
         <v>2.5656</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4695</v>
+        <v>-0.0188</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9728</v>
+        <v>-0.4231</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5033</v>
+        <v>0.4042</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3115</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1438</v>
+        <v>-4.3388</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.3559</v>
+        <v>-6.4766</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2122</v>
+        <v>2.1378</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4457</v>
@@ -1312,13 +1312,13 @@
         <v>3.1154</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5986</v>
+        <v>0.2064</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2662</v>
+        <v>-0.3869</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6676</v>
+        <v>0.5933</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6335</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.109099999999998</v>
+        <v>-7.007899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-22.5509</v>
+        <v>-21.4498</v>
       </c>
       <c r="F12" t="n">
-        <v>14.4422</v>
+        <v>14.4418</v>
       </c>
       <c r="G12" t="n">
         <v>-11.4873</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3883</v>
+        <v>-1.388300000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-10.0988</v>
@@ -1372,7 +1372,7 @@
         <v>-4.8068</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.9255</v>
+        <v>-8.925500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-3.6335</v>
@@ -1390,16 +1390,16 @@
         <v>23.8234</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6373999999999997</v>
+        <v>1.7383</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6838</v>
+        <v>-2.5827</v>
       </c>
       <c r="U12" t="n">
-        <v>4.3209</v>
+        <v>4.321099999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9241999999999998</v>
+        <v>-0.9241999999999997</v>
       </c>
       <c r="W12" t="n">
         <v>3.8529</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6369</v>
+        <v>3.5829</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4522</v>
+        <v>1.7406</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1847</v>
+        <v>1.8422</v>
       </c>
       <c r="G13" t="n">
         <v>3.4405</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.881</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4223</v>
+        <v>-0.1338</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3573</v>
+        <v>1.0149</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8381</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8094</v>
+        <v>2.6928</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.9514</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6647</v>
+        <v>3.6442</v>
       </c>
       <c r="G14" t="n">
         <v>1.3583</v>
@@ -1546,13 +1546,13 @@
         <v>3.1154</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6716</v>
+        <v>0.555</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2217</v>
+        <v>-0.3179</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8933</v>
+        <v>0.8729</v>
       </c>
       <c r="V14" t="n">
         <v>1.3293</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5233</v>
+        <v>1.5787</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4275</v>
+        <v>0.2352</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0958</v>
+        <v>1.3435</v>
       </c>
       <c r="G15" t="n">
         <v>0.9724</v>
@@ -1624,13 +1624,13 @@
         <v>2.5656</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.917</v>
+        <v>-0.8616</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2949</v>
+        <v>-0.4872</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6222</v>
+        <v>-0.3744</v>
       </c>
       <c r="V15" t="n">
         <v>1.6512</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0515</v>
+        <v>1.4152</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.3763</v>
+        <v>-0.3451</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4278</v>
+        <v>1.7604</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2607</v>
+        <v>0.761</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9467</v>
+        <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>0.314</v>
+        <v>-1.359</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1939</v>
+        <v>0.2193</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9439</v>
+        <v>2.0591</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>-1.8397</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0668</v>
+        <v>0.5416</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0029</v>
+        <v>0.0609</v>
       </c>
       <c r="O16" t="n">
-        <v>0.064</v>
+        <v>0.4807</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5814</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1154</v>
+        <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0205</v>
+        <v>-0.6731</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2662</v>
+        <v>-0.5645</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2457</v>
+        <v>-0.1086</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2774</v>
+        <v>-0.3219</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2774</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9927</v>
+        <v>1.3948</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4413</v>
+        <v>-2.5753</v>
       </c>
       <c r="F17" t="n">
-        <v>1.434</v>
+        <v>3.9701</v>
       </c>
       <c r="G17" t="n">
-        <v>0.761</v>
+        <v>2.2349</v>
       </c>
       <c r="H17" t="n">
-        <v>2.12</v>
+        <v>-1.1219</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.359</v>
+        <v>3.3568</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2193</v>
+        <v>1.8474</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0591</v>
+        <v>-0.7402</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8397</v>
+        <v>2.5876</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5416</v>
+        <v>0.3875</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0609</v>
+        <v>-0.3818</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4807</v>
+        <v>0.7692</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6493</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>3.4819</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0956</v>
+        <v>-0.7191</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6606</v>
+        <v>-0.7575</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.435</v>
+        <v>0.0384</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3219</v>
+        <v>0.0623</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.9902</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8637</v>
+        <v>-2.9917</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5446</v>
+        <v>3.9819</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2349</v>
+        <v>1.2607</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1219</v>
+        <v>0.9467</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3568</v>
+        <v>0.314</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8474</v>
+        <v>1.1939</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7402</v>
+        <v>0.9439</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5876</v>
+        <v>0.25</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3875</v>
+        <v>0.0668</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3818</v>
+        <v>0.0029</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7692</v>
+        <v>0.064</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1833</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6651</v>
+        <v>-4.5814</v>
       </c>
       <c r="R18" t="n">
-        <v>3.4819</v>
+        <v>3.1154</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.433</v>
+        <v>-0.0818</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.046</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.387</v>
+        <v>0.7997</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0623</v>
+        <v>1.2774</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2774</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0779</v>
+        <v>-0.4112</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8622</v>
+        <v>-1.7485</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7843</v>
+        <v>1.3373</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3926</v>
+        <v>0.5563</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1264</v>
+        <v>-0.2098</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2663</v>
+        <v>0.7661</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7501</v>
+        <v>0.19</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5478</v>
+        <v>0.065</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2023</v>
+        <v>0.125</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3575</v>
+        <v>0.3662</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4214</v>
+        <v>-0.2748</v>
       </c>
       <c r="O21" t="n">
-        <v>0.064</v>
+        <v>0.641</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9163</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7489</v>
+        <v>0.5498</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7158</v>
+        <v>0.3258</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4193</v>
+        <v>-0.106</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2964</v>
+        <v>0.4317</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2701</v>
+        <v>-0.0104</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9035</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4762</v>
+        <v>-0.5172</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.03</v>
+        <v>-0.7023</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5538</v>
+        <v>0.1851</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.419</v>
+        <v>-0.6682</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7748</v>
+        <v>-0.7964</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6442</v>
+        <v>0.1282</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3957</v>
+        <v>-0.6194</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2387</v>
+        <v>-0.6194</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.157</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9768</v>
+        <v>-0.0489</v>
       </c>
       <c r="N22" t="n">
-        <v>0.464</v>
+        <v>-0.1771</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5128</v>
+        <v>0.1282</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8982</v>
+        <v>0.151</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3658</v>
+        <v>-0.083</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5324</v>
+        <v>0.234</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6847</v>
+        <v>-0.5281</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8946</v>
+        <v>-2.5353</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2099</v>
+        <v>2.0073</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6682</v>
+        <v>0.3926</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7964</v>
+        <v>0.1264</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1282</v>
+        <v>0.2663</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6194</v>
+        <v>0.7501</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6194</v>
+        <v>0.5478</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.2023</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0489</v>
+        <v>-0.3575</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1771</v>
+        <v>-0.4214</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1282</v>
+        <v>0.064</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.7489</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0165</v>
+        <v>0.2656</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2753</v>
+        <v>-0.2537</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2587</v>
+        <v>0.5194</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2701</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.9035</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6851</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8446</v>
+        <v>-2.127</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1596</v>
+        <v>1.3019</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5563</v>
+        <v>-0.9943</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2098</v>
+        <v>-0.7443</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7661</v>
+        <v>-0.25</v>
       </c>
       <c r="J24" t="n">
-        <v>0.19</v>
+        <v>-1.072</v>
       </c>
       <c r="K24" t="n">
-        <v>0.065</v>
+        <v>-0.5977</v>
       </c>
       <c r="L24" t="n">
-        <v>0.125</v>
+        <v>-0.4743</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3662</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2748</v>
+        <v>-0.1466</v>
       </c>
       <c r="O24" t="n">
-        <v>0.641</v>
+        <v>0.2243</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0519</v>
+        <v>0.2242</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2021</v>
+        <v>-0.1387</v>
       </c>
       <c r="U24" t="n">
-        <v>0.254</v>
+        <v>0.3629</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.0104</v>
+        <v>0.3115</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.0104</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8062</v>
+        <v>-0.8608</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9347</v>
+        <v>-2.4146</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1285</v>
+        <v>1.5538</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9943</v>
+        <v>-1.419</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7443</v>
+        <v>-0.7748</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.25</v>
+        <v>-0.6442</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.072</v>
+        <v>-2.3957</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5977</v>
+        <v>-1.2387</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4743</v>
+        <v>-1.157</v>
       </c>
       <c r="M25" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.9768</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1466</v>
+        <v>0.464</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2243</v>
+        <v>0.5128</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3665</v>
+        <v>0.3665</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2431</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0536</v>
+        <v>-0.0188</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1895</v>
+        <v>0.5324</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3115</v>
+        <v>-0.3219</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3115</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.1309</v>
+        <v>-1.0377</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.4942</v>
+        <v>-1.3019</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3633</v>
+        <v>0.2642</v>
       </c>
       <c r="G26" t="n">
         <v>2.3168</v>
@@ -2482,13 +2482,13 @@
         <v>0.9163</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6701</v>
+        <v>-0.5769</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5784</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1006</v>
+        <v>0.0015</v>
       </c>
       <c r="V26" t="n">
         <v>-0.945</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8.109</v>
+        <v>8.7498</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.4419</v>
+        <v>-14.442</v>
       </c>
       <c r="F27" t="n">
-        <v>22.551</v>
+        <v>23.19189999999999</v>
       </c>
       <c r="G27" t="n">
         <v>11.4873</v>
@@ -2533,13 +2533,13 @@
         <v>10.099</v>
       </c>
       <c r="J27" t="n">
-        <v>8.925199999999998</v>
+        <v>8.925199999999997</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6335</v>
+        <v>3.633500000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>5.291900000000001</v>
+        <v>5.2919</v>
       </c>
       <c r="M27" t="n">
         <v>2.5618</v>
@@ -2560,19 +2560,19 @@
         <v>20.1584</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6371</v>
+        <v>0.003700000000000037</v>
       </c>
       <c r="T27" t="n">
         <v>-4.3211</v>
       </c>
       <c r="U27" t="n">
-        <v>3.6837</v>
+        <v>4.3248</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9243000000000005</v>
+        <v>0.9242999999999993</v>
       </c>
       <c r="W27" t="n">
-        <v>4.7772</v>
+        <v>4.777200000000001</v>
       </c>
       <c r="X27" t="n">
         <v>-3.8529</v>
